--- a/beam_output.xlsx
+++ b/beam_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Span (m)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Mmax (kN.m)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Deflection (mm)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Allowable Deflection (mm)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Span Check</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Stress (MPa)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Utilization</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bending Status</t>
         </is>
       </c>
     </row>
@@ -465,18 +480,29 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
         <v>45</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.9926470588235293</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>14.0625</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>0.05625</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
@@ -487,18 +513,29 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
         <v>96</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>21.33333333333333</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>0.08533333333333333</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
@@ -509,18 +546,29 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>25</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.5425347222222223</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>0.04</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
@@ -531,18 +579,29 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
         <v>187.5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>4.8828125</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>31.25</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>0.1136363636363636</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
@@ -553,18 +612,29 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
         <v>55.125</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1.480879934210526</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>14.50657894736842</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>0.05802631578947368</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>SAFE</t>
         </is>
